--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_valparaiso.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_valparaiso.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>24.79807201528075</v>
+      </c>
+      <c r="C2">
         <v>37.61885468025658</v>
-      </c>
-      <c r="C2">
-        <v>24.79807201528075</v>
       </c>
       <c r="D2">
         <v>2.658241481564371</v>
       </c>
       <c r="E2">
-        <v>23.16190525558702</v>
+        <v>15.26815740194776</v>
       </c>
       <c r="F2">
         <v>61.56993734246522</v>
       </c>
       <c r="G2">
-        <v>15.26815740194776</v>
+        <v>23.16190525558702</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>27.00722749397709</v>
+      </c>
+      <c r="C3">
         <v>33.31038890800924</v>
-      </c>
-      <c r="C3">
-        <v>27.00722749397709</v>
       </c>
       <c r="D3">
         <v>3.002066420664207</v>
       </c>
       <c r="E3">
+        <v>16.84607599595179</v>
+      </c>
+      <c r="F3">
+        <v>62.37617689453185</v>
+      </c>
+      <c r="G3">
         <v>20.77774710951636</v>
-      </c>
-      <c r="F3">
-        <v>62.37617689453184</v>
-      </c>
-      <c r="G3">
-        <v>16.84607599595179</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>24.22087308470656</v>
+      </c>
+      <c r="C4">
         <v>33.58485111303845</v>
-      </c>
-      <c r="C4">
-        <v>24.22087308470656</v>
       </c>
       <c r="D4">
         <v>2.97753292588448</v>
       </c>
       <c r="E4">
-        <v>21.28240359073005</v>
+        <v>15.34853897590913</v>
       </c>
       <c r="F4">
         <v>63.36905743336082</v>
       </c>
       <c r="G4">
-        <v>15.34853897590913</v>
+        <v>21.28240359073005</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>36.328125</v>
+      </c>
+      <c r="C5">
         <v>33.3984375</v>
-      </c>
-      <c r="C5">
-        <v>36.328125</v>
       </c>
       <c r="D5">
         <v>2.994152046783626</v>
       </c>
       <c r="E5">
-        <v>19.67779056386651</v>
+        <v>21.40391254315305</v>
       </c>
       <c r="F5">
         <v>58.91829689298044</v>
       </c>
       <c r="G5">
-        <v>21.40391254315305</v>
+        <v>19.67779056386651</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.18541400846149</v>
+      </c>
+      <c r="C6">
         <v>40.98448727419247</v>
-      </c>
-      <c r="C6">
-        <v>29.18541400846149</v>
       </c>
       <c r="D6">
         <v>2.439947566770441</v>
       </c>
       <c r="E6">
-        <v>24.08445146014207</v>
+        <v>17.1507498026835</v>
       </c>
       <c r="F6">
         <v>58.76479873717442</v>
       </c>
       <c r="G6">
-        <v>17.1507498026835</v>
+        <v>24.08445146014207</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>30.42711066871776</v>
+      </c>
+      <c r="C7">
         <v>37.93321871323862</v>
-      </c>
-      <c r="C7">
-        <v>30.42711066871776</v>
       </c>
       <c r="D7">
         <v>2.636211832061069</v>
       </c>
       <c r="E7">
-        <v>22.53097202440139</v>
+        <v>18.07261293703475</v>
       </c>
       <c r="F7">
         <v>59.39641503856387</v>
       </c>
       <c r="G7">
-        <v>18.07261293703475</v>
+        <v>22.53097202440139</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>24.14770710374237</v>
+      </c>
+      <c r="C8">
         <v>39.93742989260849</v>
-      </c>
-      <c r="C8">
-        <v>24.14770710374237</v>
       </c>
       <c r="D8">
         <v>2.503916758511987</v>
       </c>
       <c r="E8">
-        <v>24.33945610411787</v>
+        <v>14.71657186371451</v>
       </c>
       <c r="F8">
         <v>60.94397203216763</v>
       </c>
       <c r="G8">
-        <v>14.71657186371451</v>
+        <v>24.33945610411787</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>31.01876205505874</v>
+      </c>
+      <c r="C9">
         <v>19.44590566368578</v>
-      </c>
-      <c r="C9">
-        <v>31.01876205505874</v>
       </c>
       <c r="D9">
         <v>5.142470694319207</v>
       </c>
       <c r="E9">
-        <v>12.92390164316513</v>
+        <v>20.61531290059434</v>
       </c>
       <c r="F9">
         <v>66.46078545624053</v>
       </c>
       <c r="G9">
-        <v>20.61531290059434</v>
+        <v>12.92390164316513</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>27.01269223642764</v>
+      </c>
+      <c r="C10">
         <v>35.47109505280712</v>
-      </c>
-      <c r="C10">
-        <v>27.01269223642764</v>
       </c>
       <c r="D10">
         <v>2.819196865817826</v>
       </c>
       <c r="E10">
+        <v>16.62485389286427</v>
+      </c>
+      <c r="F10">
+        <v>61.54460187587308</v>
+      </c>
+      <c r="G10">
         <v>21.83054423126265</v>
-      </c>
-      <c r="F10">
-        <v>61.54460187587307</v>
-      </c>
-      <c r="G10">
-        <v>16.62485389286427</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>31.39742505403628</v>
+      </c>
+      <c r="C11">
         <v>29.14199793252514</v>
-      </c>
-      <c r="C11">
-        <v>31.39742505403628</v>
       </c>
       <c r="D11">
         <v>3.431473718155434</v>
       </c>
       <c r="E11">
-        <v>18.15254931803547</v>
+        <v>19.55745477960546</v>
       </c>
       <c r="F11">
-        <v>62.28999590235907</v>
+        <v>62.28999590235908</v>
       </c>
       <c r="G11">
-        <v>19.55745477960545</v>
+        <v>18.15254931803548</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>31.35107602190246</v>
+      </c>
+      <c r="C12">
         <v>30.98179039857379</v>
-      </c>
-      <c r="C12">
-        <v>31.35107602190246</v>
       </c>
       <c r="D12">
         <v>3.227702424989725</v>
       </c>
       <c r="E12">
-        <v>19.08534672105428</v>
+        <v>19.31283338562912</v>
       </c>
       <c r="F12">
         <v>61.6018198933166</v>
       </c>
       <c r="G12">
-        <v>19.31283338562912</v>
+        <v>19.08534672105428</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>28.34814587802635</v>
+      </c>
+      <c r="C13">
         <v>33.91051179895801</v>
-      </c>
-      <c r="C13">
-        <v>28.34814587802635</v>
       </c>
       <c r="D13">
         <v>2.948938093086308</v>
       </c>
       <c r="E13">
-        <v>20.89904617999812</v>
+        <v>17.47096043063557</v>
       </c>
       <c r="F13">
         <v>61.62999338936633</v>
       </c>
       <c r="G13">
-        <v>17.47096043063557</v>
+        <v>20.89904617999812</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>27.67238306467583</v>
+      </c>
+      <c r="C14">
         <v>38.16784823161314</v>
-      </c>
-      <c r="C14">
-        <v>27.67238306467583</v>
       </c>
       <c r="D14">
         <v>2.620006226003943</v>
       </c>
       <c r="E14">
-        <v>23.01483055907148</v>
+        <v>16.68617008573544</v>
       </c>
       <c r="F14">
         <v>60.29899935519309</v>
       </c>
       <c r="G14">
-        <v>16.68617008573544</v>
+        <v>23.01483055907148</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>26.96813830547221</v>
+      </c>
+      <c r="C15">
         <v>35.16930990141449</v>
-      </c>
-      <c r="C15">
-        <v>26.96813830547221</v>
       </c>
       <c r="D15">
         <v>2.84338817794028</v>
       </c>
       <c r="E15">
-        <v>21.69104688050757</v>
+        <v>16.63288685230878</v>
       </c>
       <c r="F15">
-        <v>61.67606626718364</v>
+        <v>61.67606626718365</v>
       </c>
       <c r="G15">
-        <v>16.63288685230878</v>
+        <v>21.69104688050758</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>27.19967030702658</v>
+      </c>
+      <c r="C16">
         <v>40.46981248712137</v>
-      </c>
-      <c r="C16">
-        <v>27.19967030702658</v>
       </c>
       <c r="D16">
         <v>2.470977596741344</v>
       </c>
       <c r="E16">
-        <v>24.1366597025931</v>
+        <v>16.22219491212978</v>
       </c>
       <c r="F16">
         <v>59.64114538527713</v>
       </c>
       <c r="G16">
-        <v>16.22219491212978</v>
+        <v>24.1366597025931</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>29.20956492859515</v>
+      </c>
+      <c r="C17">
         <v>42.42776486217203</v>
-      </c>
-      <c r="C17">
-        <v>29.20956492859515</v>
       </c>
       <c r="D17">
         <v>2.356947162426614</v>
       </c>
       <c r="E17">
-        <v>24.71942724458204</v>
+        <v>17.01818885448916</v>
       </c>
       <c r="F17">
         <v>58.2623839009288</v>
       </c>
       <c r="G17">
-        <v>17.01818885448916</v>
+        <v>24.71942724458204</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>26.80141953402252</v>
+      </c>
+      <c r="C18">
         <v>42.66316926400247</v>
-      </c>
-      <c r="C18">
-        <v>26.80141953402252</v>
       </c>
       <c r="D18">
         <v>2.343942133815552</v>
       </c>
       <c r="E18">
-        <v>25.17527087316762</v>
+        <v>15.81535099699535</v>
       </c>
       <c r="F18">
         <v>59.00937812983702</v>
       </c>
       <c r="G18">
-        <v>15.81535099699535</v>
+        <v>25.17527087316762</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>26.72102466975908</v>
+      </c>
+      <c r="C19">
         <v>35.91801357880038</v>
-      </c>
-      <c r="C19">
-        <v>26.72102466975908</v>
       </c>
       <c r="D19">
         <v>2.784118330503173</v>
       </c>
       <c r="E19">
-        <v>22.08449703441265</v>
+        <v>16.42964995213611</v>
       </c>
       <c r="F19">
         <v>61.48585301345123</v>
       </c>
       <c r="G19">
-        <v>16.42964995213611</v>
+        <v>22.08449703441265</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>28.6020846106683</v>
+      </c>
+      <c r="C20">
         <v>27.83568362967505</v>
-      </c>
-      <c r="C20">
-        <v>28.6020846106683</v>
       </c>
       <c r="D20">
         <v>3.592511013215859</v>
       </c>
       <c r="E20">
-        <v>17.79345483049186</v>
+        <v>18.28336272780717</v>
       </c>
       <c r="F20">
         <v>63.92318244170095</v>
       </c>
       <c r="G20">
-        <v>18.28336272780717</v>
+        <v>17.79345483049186</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>27.40398498411782</v>
+      </c>
+      <c r="C21">
         <v>33.44643372798151</v>
-      </c>
-      <c r="C21">
-        <v>27.40398498411782</v>
       </c>
       <c r="D21">
         <v>2.989855385279517</v>
       </c>
       <c r="E21">
-        <v>20.79350118935416</v>
+        <v>17.03693730083928</v>
       </c>
       <c r="F21">
         <v>62.16956150980656</v>
       </c>
       <c r="G21">
-        <v>17.03693730083928</v>
+        <v>20.79350118935416</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>30.22235576923077</v>
+      </c>
+      <c r="C22">
         <v>30.40264423076923</v>
-      </c>
-      <c r="C22">
-        <v>30.22235576923077</v>
       </c>
       <c r="D22">
         <v>3.289187586479541</v>
       </c>
       <c r="E22">
-        <v>18.92771625261898</v>
+        <v>18.81547440885963</v>
       </c>
       <c r="F22">
         <v>62.2568093385214</v>
       </c>
       <c r="G22">
-        <v>18.81547440885963</v>
+        <v>18.92771625261898</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>28.15070860698237</v>
+      </c>
+      <c r="C23">
         <v>39.23263048738334</v>
-      </c>
-      <c r="C23">
-        <v>28.15070860698237</v>
       </c>
       <c r="D23">
         <v>2.548898678414097</v>
       </c>
       <c r="E23">
-        <v>23.43879068230629</v>
+        <v>16.81810672393854</v>
       </c>
       <c r="F23">
         <v>59.74310259375516</v>
       </c>
       <c r="G23">
-        <v>16.81810672393854</v>
+        <v>23.43879068230629</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>28.02662092188443</v>
+      </c>
+      <c r="C24">
         <v>35.03923250420915</v>
-      </c>
-      <c r="C24">
-        <v>28.02662092188443</v>
       </c>
       <c r="D24">
         <v>2.853943789664551</v>
       </c>
       <c r="E24">
-        <v>21.48778040774183</v>
+        <v>17.18730214390774</v>
       </c>
       <c r="F24">
         <v>61.32491744835042</v>
       </c>
       <c r="G24">
-        <v>17.18730214390774</v>
+        <v>21.48778040774183</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>26.82531559194814</v>
+      </c>
+      <c r="C25">
         <v>52.7294438758103</v>
-      </c>
-      <c r="C25">
-        <v>26.82531559194814</v>
       </c>
       <c r="D25">
         <v>1.896473633128437</v>
       </c>
       <c r="E25">
-        <v>29.3667759251342</v>
+        <v>14.93990784285782</v>
       </c>
       <c r="F25">
         <v>55.69331623200799</v>
       </c>
       <c r="G25">
-        <v>14.93990784285782</v>
+        <v>29.3667759251342</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>31.13412607083493</v>
+      </c>
+      <c r="C26">
         <v>44.54673315432809</v>
-      </c>
-      <c r="C26">
-        <v>31.13412607083493</v>
       </c>
       <c r="D26">
         <v>2.244833524684271</v>
       </c>
       <c r="E26">
-        <v>25.3566229985444</v>
+        <v>17.72197962154295</v>
       </c>
       <c r="F26">
         <v>56.92139737991267</v>
       </c>
       <c r="G26">
-        <v>17.72197962154295</v>
+        <v>25.3566229985444</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>27.97467313543294</v>
+      </c>
+      <c r="C27">
         <v>53.72091110928378</v>
-      </c>
-      <c r="C27">
-        <v>27.97467313543294</v>
       </c>
       <c r="D27">
         <v>1.861472524108373</v>
       </c>
       <c r="E27">
-        <v>29.56643736422882</v>
+        <v>15.39645184648805</v>
       </c>
       <c r="F27">
         <v>55.03711078928313</v>
       </c>
       <c r="G27">
-        <v>15.39645184648805</v>
+        <v>29.56643736422882</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>27.0404984423676</v>
+      </c>
+      <c r="C28">
         <v>57.84601691143747</v>
-      </c>
-      <c r="C28">
-        <v>27.0404984423676</v>
       </c>
       <c r="D28">
         <v>1.728727496537929</v>
       </c>
       <c r="E28">
-        <v>31.28730984016946</v>
+        <v>14.62545734642788</v>
       </c>
       <c r="F28">
         <v>54.08723281340266</v>
       </c>
       <c r="G28">
-        <v>14.62545734642788</v>
+        <v>31.28730984016946</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>25.16353229762878</v>
+      </c>
+      <c r="C29">
         <v>37.88838920686835</v>
-      </c>
-      <c r="C29">
-        <v>25.16353229762878</v>
       </c>
       <c r="D29">
         <v>2.639330995414082</v>
       </c>
       <c r="E29">
-        <v>23.23700871309472</v>
+        <v>15.43283394972732</v>
       </c>
       <c r="F29">
-        <v>61.33015733717797</v>
+        <v>61.33015733717795</v>
       </c>
       <c r="G29">
-        <v>15.43283394972733</v>
+        <v>23.23700871309471</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>28.56509417593645</v>
+      </c>
+      <c r="C30">
         <v>31.94270401573133</v>
-      </c>
-      <c r="C30">
-        <v>28.56509417593645</v>
       </c>
       <c r="D30">
         <v>3.130605347335385</v>
       </c>
       <c r="E30">
-        <v>19.90102934287808</v>
+        <v>17.79670177882941</v>
       </c>
       <c r="F30">
         <v>62.30226887829252</v>
       </c>
       <c r="G30">
-        <v>17.79670177882941</v>
+        <v>19.90102934287808</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>29.48140387637507</v>
+      </c>
+      <c r="C31">
         <v>35.65217391304348</v>
-      </c>
-      <c r="C31">
-        <v>29.48140387637507</v>
       </c>
       <c r="D31">
         <v>2.804878048780488</v>
       </c>
       <c r="E31">
+        <v>17.85306433193758</v>
+      </c>
+      <c r="F31">
+        <v>60.5570359091486</v>
+      </c>
+      <c r="G31">
         <v>21.58989975891384</v>
-      </c>
-      <c r="F31">
-        <v>60.55703590914858</v>
-      </c>
-      <c r="G31">
-        <v>17.85306433193757</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>33.321854912764</v>
+      </c>
+      <c r="C32">
         <v>20.67263544536272</v>
-      </c>
-      <c r="C32">
-        <v>33.321854912764</v>
       </c>
       <c r="D32">
         <v>4.837312604108829</v>
       </c>
       <c r="E32">
-        <v>13.42426952892069</v>
+        <v>21.63834227787716</v>
       </c>
       <c r="F32">
         <v>64.93738819320215</v>
       </c>
       <c r="G32">
-        <v>21.63834227787716</v>
+        <v>13.42426952892069</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>20.01121862291404</v>
+      </c>
+      <c r="C33">
         <v>25.76076286635816</v>
-      </c>
-      <c r="C33">
-        <v>20.01121862291404</v>
       </c>
       <c r="D33">
         <v>3.881872618399564</v>
       </c>
       <c r="E33">
-        <v>17.67195767195767</v>
+        <v>13.72775372775373</v>
       </c>
       <c r="F33">
         <v>68.60028860028859</v>
       </c>
       <c r="G33">
-        <v>13.72775372775373</v>
+        <v>17.67195767195767</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>28.83402894947163</v>
+      </c>
+      <c r="C34">
         <v>39.99644791759169</v>
-      </c>
-      <c r="C34">
-        <v>28.83402894947163</v>
       </c>
       <c r="D34">
         <v>2.500222024866785</v>
       </c>
       <c r="E34">
-        <v>23.69030086261308</v>
+        <v>17.07868714496108</v>
       </c>
       <c r="F34">
         <v>59.23101199242583</v>
       </c>
       <c r="G34">
-        <v>17.07868714496108</v>
+        <v>23.69030086261308</v>
       </c>
     </row>
     <row r="35">
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="B35">
+        <v>29.17214191852825</v>
+      </c>
+      <c r="C35">
         <v>35.89406651167492</v>
-      </c>
-      <c r="C35">
-        <v>29.17214191852825</v>
       </c>
       <c r="D35">
         <v>2.785975781470008</v>
       </c>
       <c r="E35">
-        <v>21.74525413349663</v>
+        <v>17.67299448867116</v>
       </c>
       <c r="F35">
         <v>60.58175137783221</v>
       </c>
       <c r="G35">
-        <v>17.67299448867116</v>
+        <v>21.74525413349663</v>
       </c>
     </row>
     <row r="36">
@@ -1248,22 +1248,22 @@
         </is>
       </c>
       <c r="B36">
+        <v>24.69725725185692</v>
+      </c>
+      <c r="C36">
         <v>39.60848161385728</v>
-      </c>
-      <c r="C36">
-        <v>24.69725725185692</v>
       </c>
       <c r="D36">
         <v>2.524711777010264</v>
       </c>
       <c r="E36">
-        <v>24.1065722276621</v>
+        <v>15.03128096581081</v>
       </c>
       <c r="F36">
         <v>60.86214680652708</v>
       </c>
       <c r="G36">
-        <v>15.03128096581081</v>
+        <v>24.1065722276621</v>
       </c>
     </row>
     <row r="37">
@@ -1273,22 +1273,22 @@
         </is>
       </c>
       <c r="B37">
+        <v>28.32943756673304</v>
+      </c>
+      <c r="C37">
         <v>35.90742504256485</v>
-      </c>
-      <c r="C37">
-        <v>28.32943756673304</v>
       </c>
       <c r="D37">
         <v>2.784939323314313</v>
       </c>
       <c r="E37">
-        <v>21.8631947006835</v>
+        <v>17.24913464410592</v>
       </c>
       <c r="F37">
         <v>60.88767065521058</v>
       </c>
       <c r="G37">
-        <v>17.24913464410592</v>
+        <v>21.8631947006835</v>
       </c>
     </row>
     <row r="38">
@@ -1298,22 +1298,22 @@
         </is>
       </c>
       <c r="B38">
+        <v>28.33602584814216</v>
+      </c>
+      <c r="C38">
         <v>44.11147011308562</v>
-      </c>
-      <c r="C38">
-        <v>28.33602584814216</v>
       </c>
       <c r="D38">
         <v>2.266984068851859</v>
       </c>
       <c r="E38">
-        <v>25.57965244273737</v>
+        <v>16.4316829828095</v>
       </c>
       <c r="F38">
         <v>57.98866457445314</v>
       </c>
       <c r="G38">
-        <v>16.4316829828095</v>
+        <v>25.57965244273737</v>
       </c>
     </row>
     <row r="39">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="B39">
+        <v>28.11441112276767</v>
+      </c>
+      <c r="C39">
         <v>36.48783899480279</v>
-      </c>
-      <c r="C39">
-        <v>28.11441112276767</v>
       </c>
       <c r="D39">
         <v>2.740639148683036</v>
       </c>
       <c r="E39">
-        <v>22.16727837483425</v>
+        <v>17.08021069134012</v>
       </c>
       <c r="F39">
         <v>60.75251093382563</v>
       </c>
       <c r="G39">
-        <v>17.08021069134012</v>
+        <v>22.16727837483425</v>
       </c>
     </row>
   </sheetData>
